--- a/Analysis/Phase1_Results_with_WES.xlsx
+++ b/Analysis/Phase1_Results_with_WES.xlsx
@@ -2450,11 +2450,15 @@
       </c>
       <c r="E54" t="inlineStr"/>
       <c r="F54" t="inlineStr"/>
-      <c r="G54" t="inlineStr"/>
-      <c r="H54" t="inlineStr"/>
+      <c r="G54" t="n">
+        <v>0</v>
+      </c>
+      <c r="H54" t="n">
+        <v>0</v>
+      </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>Build failure</t>
+          <t>Perfect</t>
         </is>
       </c>
     </row>
@@ -2477,11 +2481,15 @@
       </c>
       <c r="E55" t="inlineStr"/>
       <c r="F55" t="inlineStr"/>
-      <c r="G55" t="inlineStr"/>
-      <c r="H55" t="inlineStr"/>
+      <c r="G55" t="n">
+        <v>0</v>
+      </c>
+      <c r="H55" t="n">
+        <v>0</v>
+      </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>Build failure</t>
+          <t>Perfect</t>
         </is>
       </c>
     </row>
